--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12135"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>零件名称：</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>肘关节连接B</t>
+  </si>
+  <si>
+    <t>钣金快拆</t>
   </si>
 </sst>
 </file>
@@ -524,7 +527,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -571,6 +574,30 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F2329"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -695,7 +722,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -707,34 +734,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -819,7 +846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -862,6 +889,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1676,6 +1727,44 @@
         <a:ln w="9525">
           <a:noFill/>
         </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2" descr="钣金快拆"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2409825" y="30718125"/>
+          <a:ext cx="3006725" cy="2133600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2000,7 +2089,7 @@
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2338,25 +2427,43 @@
       <c r="H21" s="14"/>
     </row>
     <row r="22" ht="165" customHeight="1" spans="1:11">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="10">
+      <c r="C22" s="17"/>
+      <c r="D22" s="18">
         <v>4</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="18">
         <v>2</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="18">
         <v>8</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="20"/>
     </row>
-    <row r="23" ht="165" customHeight="1"/>
+    <row r="23" ht="165" customHeight="1" spans="1:11">
+      <c r="B23" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23">
+        <v>2</v>
+      </c>
+      <c r="E23" s="23">
+        <v>2</v>
+      </c>
+      <c r="F23" s="23">
+        <v>4</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="22"/>
+    </row>
     <row r="24" ht="165" customHeight="1"/>
     <row r="25" ht="165" customHeight="1"/>
     <row r="26" ht="165" customHeight="1"/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>零件名称：</t>
   </si>
@@ -68,58 +68,52 @@
     <t>大腿内侧-L</t>
   </si>
   <si>
+    <t>6061合金</t>
+  </si>
+  <si>
+    <t>大腿内侧-R</t>
+  </si>
+  <si>
+    <t>大腿外侧-L</t>
+  </si>
+  <si>
+    <t>大腿外侧-R</t>
+  </si>
+  <si>
+    <t>4530快拆法兰-A</t>
+  </si>
+  <si>
+    <t>横梁</t>
+  </si>
+  <si>
+    <t>髋关节快拆</t>
+  </si>
+  <si>
+    <t>钢连杆</t>
+  </si>
+  <si>
+    <t>7075合金</t>
+  </si>
+  <si>
+    <t>箱体侧板</t>
+  </si>
+  <si>
+    <t>摇臂</t>
+  </si>
+  <si>
+    <t>45钢</t>
+  </si>
+  <si>
+    <t>4530快拆法兰-B</t>
+  </si>
+  <si>
+    <t>4530快拆法兰-C</t>
+  </si>
+  <si>
+    <t>钣金快拆</t>
+  </si>
+  <si>
     <t>镀锌板</t>
-  </si>
-  <si>
-    <t>大腿内侧-R</t>
-  </si>
-  <si>
-    <t>大腿外侧-L</t>
-  </si>
-  <si>
-    <t>大腿外侧-R</t>
-  </si>
-  <si>
-    <t>大小腿电机连接块</t>
-  </si>
-  <si>
-    <t>6061合金</t>
-  </si>
-  <si>
-    <t>横梁</t>
-  </si>
-  <si>
-    <t>快拆法兰01</t>
-  </si>
-  <si>
-    <t>快拆法兰02</t>
-  </si>
-  <si>
-    <t>髋关节连接</t>
-  </si>
-  <si>
-    <t>连杆</t>
-  </si>
-  <si>
-    <t>7075合金</t>
-  </si>
-  <si>
-    <t>箱体侧板</t>
-  </si>
-  <si>
-    <t>摇臂</t>
-  </si>
-  <si>
-    <t>45钢</t>
-  </si>
-  <si>
-    <t>肘关节连接A</t>
-  </si>
-  <si>
-    <t>肘关节连接B</t>
-  </si>
-  <si>
-    <t>钣金快拆</t>
   </si>
 </sst>
 </file>
@@ -846,7 +840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -907,12 +901,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1104,19 +1092,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>16510</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2966720</xdr:colOff>
+      <xdr:colOff>2936875</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>2082165</xdr:rowOff>
+      <xdr:rowOff>2070735</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPr id="7" name="图片 6"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1129,8 +1117,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2451100" y="1388110"/>
-          <a:ext cx="2915920" cy="2065655"/>
+          <a:off x="2571750" y="1371600"/>
+          <a:ext cx="2765425" cy="2070735"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1146,19 +1134,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>64770</xdr:colOff>
+      <xdr:colOff>69215</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2956560</xdr:colOff>
+      <xdr:colOff>2910840</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>2067560</xdr:rowOff>
+      <xdr:rowOff>2056765</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPr id="10" name="图片 9"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1171,8 +1159,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2465070" y="3489325"/>
-          <a:ext cx="2891790" cy="2045335"/>
+          <a:off x="2469515" y="3514725"/>
+          <a:ext cx="2841625" cy="2009140"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1188,19 +1176,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>34290</xdr:colOff>
+      <xdr:colOff>117475</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>6985</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2963545</xdr:colOff>
+      <xdr:colOff>2931795</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2078990</xdr:rowOff>
+      <xdr:rowOff>2007235</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPr id="11" name="图片 10"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1213,8 +1201,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2434590" y="5569585"/>
-          <a:ext cx="2929255" cy="2072005"/>
+          <a:off x="2517775" y="5572125"/>
+          <a:ext cx="2814320" cy="1997710"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1230,19 +1218,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>26035</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>13970</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2971800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>3175</xdr:rowOff>
+      <xdr:colOff>2955290</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>2086610</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="图片 15"/>
+        <xdr:cNvPr id="17" name="图片 16"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1255,8 +1243,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2426335" y="7672070"/>
-          <a:ext cx="2945765" cy="2084705"/>
+          <a:off x="2457450" y="7686675"/>
+          <a:ext cx="2898140" cy="2058035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1272,19 +1260,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>27305</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>24130</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2955290</xdr:colOff>
+      <xdr:colOff>2851150</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>2094865</xdr:rowOff>
+      <xdr:rowOff>2049145</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="图片 18"/>
+        <xdr:cNvPr id="18" name="图片 17"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1297,8 +1285,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2427605" y="9777730"/>
-          <a:ext cx="2927985" cy="2070735"/>
+          <a:off x="2447925" y="9810750"/>
+          <a:ext cx="2803525" cy="1991995"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1314,19 +1302,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>27940</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>12065</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2954655</xdr:colOff>
+      <xdr:colOff>2912110</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>2080895</xdr:rowOff>
+      <xdr:rowOff>2063115</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="图片 19"/>
+        <xdr:cNvPr id="21" name="图片 20"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1339,8 +1327,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2428240" y="11861165"/>
-          <a:ext cx="2926715" cy="2068830"/>
+          <a:off x="2457450" y="11906250"/>
+          <a:ext cx="2854960" cy="2005965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1356,19 +1344,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>31115</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>14605</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2952115</xdr:colOff>
+      <xdr:colOff>2823845</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2083435</xdr:rowOff>
+      <xdr:rowOff>2037715</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="图片 22"/>
+        <xdr:cNvPr id="22" name="图片 21"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1381,8 +1369,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2431415" y="13959205"/>
-          <a:ext cx="2921000" cy="2068830"/>
+          <a:off x="2400300" y="13982700"/>
+          <a:ext cx="2823845" cy="1999615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1398,19 +1386,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>43180</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2961005</xdr:colOff>
+      <xdr:colOff>2894965</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>2069465</xdr:rowOff>
+      <xdr:rowOff>2076450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="图片 23"/>
+        <xdr:cNvPr id="28" name="图片 27"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1423,8 +1411,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2443480" y="16046450"/>
-          <a:ext cx="2917825" cy="2063115"/>
+          <a:off x="2419350" y="16087725"/>
+          <a:ext cx="2875915" cy="2028825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1440,19 +1428,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>31115</xdr:colOff>
+      <xdr:colOff>66675</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2958465</xdr:colOff>
+      <xdr:colOff>2908300</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2072005</xdr:rowOff>
+      <xdr:rowOff>2060575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="图片 24"/>
+        <xdr:cNvPr id="29" name="图片 28"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1465,8 +1453,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2431415" y="18148300"/>
-          <a:ext cx="2927350" cy="2059305"/>
+          <a:off x="2466975" y="18183225"/>
+          <a:ext cx="2841625" cy="2012950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1482,19 +1470,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2969260</xdr:colOff>
+      <xdr:colOff>2940050</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>2073275</xdr:rowOff>
+      <xdr:rowOff>2080260</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="图片 25"/>
+        <xdr:cNvPr id="30" name="图片 29"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1507,8 +1495,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2463800" y="20237450"/>
-          <a:ext cx="2905760" cy="2066925"/>
+          <a:off x="2447925" y="20269200"/>
+          <a:ext cx="2892425" cy="2042160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,19 +1512,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>53975</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2904490</xdr:colOff>
+      <xdr:colOff>2915920</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>2063750</xdr:rowOff>
+      <xdr:rowOff>2067560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="图片 26"/>
+        <xdr:cNvPr id="31" name="图片 30"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1549,8 +1537,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2482850" y="22380575"/>
-          <a:ext cx="2821940" cy="2009775"/>
+          <a:off x="2428875" y="22355175"/>
+          <a:ext cx="2887345" cy="2038985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1566,33 +1554,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>53975</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2904490</xdr:colOff>
+      <xdr:colOff>2912110</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>2063750</xdr:rowOff>
+      <xdr:rowOff>2052320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPr id="32" name="图片 31"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2482850" y="24476075"/>
-          <a:ext cx="2821940" cy="2009775"/>
+          <a:off x="2428875" y="24431625"/>
+          <a:ext cx="2883535" cy="2042795"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1608,61 +1596,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>19685</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2935605</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2073275</xdr:rowOff>
+      <xdr:colOff>2870200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2071370</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2432050" y="24441785"/>
-          <a:ext cx="2903855" cy="2053590"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>35560</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2963545</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2091055</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPr id="33" name="图片 32"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1675,8 +1621,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="26553160"/>
-          <a:ext cx="2906395" cy="2055495"/>
+          <a:off x="2400300" y="26565225"/>
+          <a:ext cx="2870200" cy="2023745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1685,86 +1631,6 @@
         <a:ln w="9525">
           <a:noFill/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2948940</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2073275</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2457450" y="28641675"/>
-          <a:ext cx="2891790" cy="2044700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>15875</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="钣金快拆"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2409825" y="30718125"/>
-          <a:ext cx="3006725" cy="2133600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2032,7 +1898,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -2251,23 +2117,23 @@
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13" s="10">
         <v>2</v>
       </c>
       <c r="F13" s="10">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H13" s="14"/>
     </row>
     <row r="14" ht="165" customHeight="1" spans="1:21">
       <c r="A14" s="1"/>
       <c r="B14" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="10">
@@ -2280,14 +2146,14 @@
         <v>4</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H14" s="14"/>
     </row>
     <row r="15" ht="165" customHeight="1" spans="1:21">
       <c r="A15" s="1"/>
       <c r="B15" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="10">
@@ -2300,14 +2166,15 @@
         <v>8</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H15" s="14"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" ht="165" customHeight="1" spans="1:21">
       <c r="A16" s="1"/>
       <c r="B16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="10">
@@ -2320,7 +2187,7 @@
         <v>8</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H16" s="14"/>
       <c r="K16" s="1"/>
@@ -2332,22 +2199,21 @@
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
       </c>
       <c r="F17" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14"/>
       <c r="K17" s="1"/>
     </row>
     <row r="18" ht="165" customHeight="1" spans="1:11">
-      <c r="A18" s="1"/>
       <c r="B18" s="8" t="s">
         <v>23</v>
       </c>
@@ -2365,111 +2231,70 @@
         <v>24</v>
       </c>
       <c r="H18" s="14"/>
-      <c r="K18" s="1"/>
     </row>
     <row r="19" ht="165" customHeight="1" spans="1:11">
-      <c r="A19" s="1"/>
       <c r="B19" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
       </c>
       <c r="F19" s="10">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H19" s="14"/>
-      <c r="K19" s="1"/>
     </row>
     <row r="20" ht="165" customHeight="1" spans="1:11">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="10">
+      <c r="C20" s="17"/>
+      <c r="D20" s="18">
         <v>4</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="18">
         <v>2</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="18">
         <v>8</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="14"/>
+      <c r="G20" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" ht="165" customHeight="1" spans="1:11">
-      <c r="B21" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="13"/>
+      <c r="B21" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="9"/>
       <c r="D21" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
       </c>
       <c r="F21" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="14"/>
+        <v>28</v>
+      </c>
+      <c r="H21" s="9"/>
     </row>
-    <row r="22" ht="165" customHeight="1" spans="1:11">
-      <c r="B22" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18">
-        <v>4</v>
-      </c>
-      <c r="E22" s="18">
-        <v>2</v>
-      </c>
-      <c r="F22" s="18">
-        <v>8</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="20"/>
-    </row>
-    <row r="23" ht="165" customHeight="1" spans="1:11">
-      <c r="B23" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="23">
-        <v>2</v>
-      </c>
-      <c r="E23" s="23">
-        <v>2</v>
-      </c>
-      <c r="F23" s="23">
-        <v>4</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="22"/>
-    </row>
+    <row r="22" ht="165" customHeight="1"/>
+    <row r="23" ht="165" customHeight="1"/>
     <row r="24" ht="165" customHeight="1"/>
     <row r="25" ht="165" customHeight="1"/>
     <row r="26" ht="165" customHeight="1"/>
     <row r="27" ht="165" customHeight="1"/>
-    <row r="28" ht="165" customHeight="1"/>
-    <row r="29" ht="165" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -2041,10 +2041,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>13</v>
@@ -2061,10 +2061,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>13</v>
@@ -2080,10 +2080,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>13</v>
@@ -2100,10 +2100,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>13</v>
@@ -2120,10 +2120,10 @@
         <v>8</v>
       </c>
       <c r="E13" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" s="10">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>13</v>
@@ -2140,10 +2140,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>13</v>
@@ -2160,10 +2160,10 @@
         <v>4</v>
       </c>
       <c r="E15" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F15" s="10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>13</v>
@@ -2181,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" s="10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>21</v>
@@ -2202,10 +2202,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>13</v>
@@ -2222,10 +2222,10 @@
         <v>4</v>
       </c>
       <c r="E18" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F18" s="10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>24</v>
@@ -2241,10 +2241,10 @@
         <v>8</v>
       </c>
       <c r="E19" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19" s="10">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>13</v>
@@ -2260,10 +2260,10 @@
         <v>4</v>
       </c>
       <c r="E20" s="18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" s="18">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>13</v>
@@ -2279,10 +2279,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>28</v>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>零件名称：</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>镀锌板</t>
+  </si>
+  <si>
+    <t>限位块</t>
+  </si>
+  <si>
+    <t>大腿限位块</t>
   </si>
 </sst>
 </file>
@@ -142,13 +148,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -163,6 +162,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
@@ -521,7 +527,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -592,6 +598,19 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -716,7 +735,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,34 +747,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -840,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -855,52 +874,70 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1513,48 +1550,6 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2915920</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2067560</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="图片 30"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2428875" y="22355175"/>
-          <a:ext cx="2887345" cy="2038985"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
@@ -1572,7 +1567,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
+        <a:blip r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1614,7 +1609,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
+        <a:blip r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1623,6 +1618,132 @@
         <a:xfrm>
           <a:off x="2400300" y="26565225"/>
           <a:ext cx="2870200" cy="2023745"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2886710</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2004695</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2667000" y="22355175"/>
+          <a:ext cx="2620010" cy="1976120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2922905</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2047875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2638425" y="28632150"/>
+          <a:ext cx="2684780" cy="2028825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2858135</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2091055</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2571750" y="30756225"/>
+          <a:ext cx="2686685" cy="2043430"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1912,7 +2033,7 @@
     <col min="9" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:21">
+    <row r="1" ht="13.5" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1925,7 +2046,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="13.5" spans="1:21">
+    <row r="2" ht="13.5" spans="1:8">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -1935,7 +2056,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" ht="13.5" spans="1:21">
+    <row r="3" ht="13.5" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1949,13 +2070,13 @@
       <c r="G3" s="1"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" ht="13.5" spans="1:21">
+    <row r="4" ht="13.5" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46265</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1964,7 +2085,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" ht="13.5" spans="1:21">
+    <row r="5" ht="13.5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
@@ -1974,7 +2095,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" ht="13.5" spans="1:21">
+    <row r="6" ht="13.5" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -2009,288 +2130,320 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
     </row>
-    <row r="8" ht="13.5" spans="1:21">
+    <row r="8" ht="13.5" spans="1:8">
       <c r="A8" s="1"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6"/>
     </row>
-    <row r="9" ht="165" customHeight="1" spans="1:21">
+    <row r="9" ht="165" customHeight="1" spans="1:8">
       <c r="A9" s="1"/>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10">
+      <c r="C9" s="8"/>
+      <c r="D9" s="9">
         <v>2</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>5</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>10</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="11"/>
     </row>
-    <row r="10" ht="165" customHeight="1" spans="1:21">
+    <row r="10" ht="165" customHeight="1" spans="1:8">
       <c r="A10" s="1"/>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="10">
+      <c r="C10" s="12"/>
+      <c r="D10" s="9">
         <v>2</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>5</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>10</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="11"/>
+      <c r="H10" s="10"/>
     </row>
-    <row r="11" ht="165" customHeight="1" spans="1:21">
-      <c r="B11" s="8" t="s">
+    <row r="11" ht="165" customHeight="1" spans="2:8">
+      <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="10">
+      <c r="C11" s="13"/>
+      <c r="D11" s="9">
         <v>2</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>5</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>10</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="10"/>
     </row>
-    <row r="12" ht="165" customHeight="1" spans="1:21">
+    <row r="12" ht="165" customHeight="1" spans="1:8">
       <c r="A12" s="1"/>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="10">
+      <c r="C12" s="12"/>
+      <c r="D12" s="9">
         <v>2</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>5</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>10</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="10"/>
     </row>
-    <row r="13" ht="165" customHeight="1" spans="1:21">
+    <row r="13" ht="165" customHeight="1" spans="1:8">
       <c r="A13" s="1"/>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="10">
+      <c r="C13" s="12"/>
+      <c r="D13" s="9">
         <v>8</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>5</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>40</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="13"/>
     </row>
-    <row r="14" ht="165" customHeight="1" spans="1:21">
+    <row r="14" ht="165" customHeight="1" spans="1:8">
       <c r="A14" s="1"/>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="10">
+      <c r="C14" s="12"/>
+      <c r="D14" s="9">
         <v>2</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>5</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>10</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="13"/>
     </row>
-    <row r="15" ht="165" customHeight="1" spans="1:21">
+    <row r="15" ht="165" customHeight="1" spans="1:11">
       <c r="A15" s="1"/>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="10">
+      <c r="C15" s="12"/>
+      <c r="D15" s="9">
         <v>4</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>5</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>20</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="13"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" ht="165" customHeight="1" spans="1:21">
+    <row r="16" ht="165" customHeight="1" spans="1:11">
       <c r="A16" s="1"/>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="10">
+      <c r="C16" s="12"/>
+      <c r="D16" s="9">
         <v>4</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>5</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>20</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="14"/>
+      <c r="H16" s="13"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" ht="165" customHeight="1" spans="1:11">
       <c r="A17" s="1"/>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="10">
+      <c r="C17" s="12"/>
+      <c r="D17" s="9">
         <v>2</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>5</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>10</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="13"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" ht="165" customHeight="1" spans="1:11">
-      <c r="B18" s="8" t="s">
+    <row r="18" ht="165" customHeight="1" spans="2:8">
+      <c r="B18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="10">
+      <c r="C18" s="12"/>
+      <c r="D18" s="9">
         <v>4</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>5</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>20</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="13"/>
     </row>
-    <row r="19" ht="165" customHeight="1" spans="1:11">
-      <c r="B19" s="8" t="s">
+    <row r="19" ht="165" customHeight="1" spans="2:8">
+      <c r="B19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="10">
+      <c r="C19" s="12"/>
+      <c r="D19" s="9">
         <v>8</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>5</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>40</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="14"/>
+      <c r="H19" s="13"/>
     </row>
-    <row r="20" ht="165" customHeight="1" spans="1:11">
-      <c r="B20" s="16" t="s">
+    <row r="20" ht="165" customHeight="1" spans="2:8">
+      <c r="B20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18">
+      <c r="C20" s="16"/>
+      <c r="D20" s="17">
         <v>4</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>5</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <v>20</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="20"/>
+      <c r="H20" s="19"/>
     </row>
-    <row r="21" ht="165" customHeight="1" spans="1:11">
-      <c r="B21" s="21" t="s">
+    <row r="21" ht="165" customHeight="1" spans="2:8">
+      <c r="B21" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10">
+      <c r="C21" s="8"/>
+      <c r="D21" s="9">
         <v>2</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>5</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>10</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="9"/>
+      <c r="H21" s="8"/>
     </row>
-    <row r="22" ht="165" customHeight="1"/>
-    <row r="23" ht="165" customHeight="1"/>
+    <row r="22" ht="165" customHeight="1" spans="2:8">
+      <c r="B22" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="22">
+        <v>8</v>
+      </c>
+      <c r="E22" s="22">
+        <v>5</v>
+      </c>
+      <c r="F22" s="22">
+        <v>40</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="23"/>
+    </row>
+    <row r="23" ht="165" customHeight="1" spans="2:8">
+      <c r="B23" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25">
+        <v>8</v>
+      </c>
+      <c r="E23" s="25">
+        <v>5</v>
+      </c>
+      <c r="F23" s="25">
+        <v>40</v>
+      </c>
+      <c r="G23" s="24"/>
+      <c r="H23" s="26"/>
+    </row>
     <row r="24" ht="165" customHeight="1"/>
     <row r="25" ht="165" customHeight="1"/>
     <row r="26" ht="165" customHeight="1"/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -859,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -926,15 +926,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1381,48 +1372,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2823845</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>2037715</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="图片 21"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2400300" y="13982700"/>
-          <a:ext cx="2823845" cy="1999615"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -1441,7 +1390,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
+        <a:blip r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1483,7 +1432,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
+        <a:blip r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1525,7 +1474,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
+        <a:blip r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1567,7 +1516,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1609,7 +1558,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
+        <a:blip r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1651,7 +1600,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
+        <a:blip r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1693,7 +1642,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
+        <a:blip r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1735,7 +1684,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
+        <a:blip r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1744,6 +1693,48 @@
         <a:xfrm>
           <a:off x="2571750" y="30756225"/>
           <a:ext cx="2686685" cy="2043430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2794635</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2049145</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2457450" y="13944600"/>
+          <a:ext cx="2737485" cy="2049145"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2130,19 +2121,19 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="27"/>
-      <c r="U7" s="27"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
     </row>
     <row r="8" ht="13.5" spans="1:8">
       <c r="A8" s="1"/>
@@ -2428,21 +2419,21 @@
       <c r="H22" s="23"/>
     </row>
     <row r="23" ht="165" customHeight="1" spans="2:8">
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="25">
+      <c r="C23" s="20"/>
+      <c r="D23" s="9">
         <v>8</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="9">
         <v>5</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="9">
         <v>40</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="26"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" ht="165" customHeight="1"/>
     <row r="25" ht="165" customHeight="1"/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -1624,19 +1624,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2922905</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2047875</xdr:rowOff>
+      <xdr:colOff>2794635</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2049145</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="5" name="图片 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1649,8 +1649,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2638425" y="28632150"/>
-          <a:ext cx="2684780" cy="2028825"/>
+          <a:off x="2457450" y="13944600"/>
+          <a:ext cx="2737485" cy="2049145"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1666,19 +1666,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2858135</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>2091055</xdr:rowOff>
+      <xdr:colOff>2951480</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2085975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPr id="6" name="图片 5"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1691,8 +1691,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2571750" y="30756225"/>
-          <a:ext cx="2686685" cy="2043430"/>
+          <a:off x="2619375" y="28641675"/>
+          <a:ext cx="2732405" cy="2057400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1708,19 +1708,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2794635</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>2049145</xdr:rowOff>
+      <xdr:colOff>2934335</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2067560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPr id="8" name="图片 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1733,8 +1733,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="13944600"/>
-          <a:ext cx="2737485" cy="2049145"/>
+          <a:off x="2657475" y="30746700"/>
+          <a:ext cx="2677160" cy="2029460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -1666,19 +1666,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
+      <xdr:colOff>209550</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2951480</xdr:colOff>
+      <xdr:colOff>2873375</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>2085975</xdr:rowOff>
+      <xdr:rowOff>2038985</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1691,8 +1691,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2619375" y="28641675"/>
-          <a:ext cx="2732405" cy="2057400"/>
+          <a:off x="2609850" y="28641675"/>
+          <a:ext cx="2663825" cy="2010410"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1708,19 +1708,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2934335</xdr:colOff>
+      <xdr:colOff>2857500</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>2067560</xdr:rowOff>
+      <xdr:rowOff>2081530</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPr id="4" name="图片 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1733,8 +1733,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2657475" y="30746700"/>
-          <a:ext cx="2677160" cy="2029460"/>
+          <a:off x="2552700" y="30756225"/>
+          <a:ext cx="2705100" cy="2033905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>零件名称：</t>
   </si>
@@ -1666,19 +1666,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2873375</xdr:colOff>
+      <xdr:colOff>2869565</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>2038985</xdr:rowOff>
+      <xdr:rowOff>2089785</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="6" name="图片 5"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1691,8 +1691,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2609850" y="28641675"/>
-          <a:ext cx="2663825" cy="2010410"/>
+          <a:off x="2543175" y="28641675"/>
+          <a:ext cx="2726690" cy="2061210"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1708,19 +1708,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2857500</xdr:colOff>
+      <xdr:colOff>2729230</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>2081530</xdr:rowOff>
+      <xdr:rowOff>2056765</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPr id="8" name="图片 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1733,8 +1733,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2552700" y="30756225"/>
-          <a:ext cx="2705100" cy="2033905"/>
+          <a:off x="2486025" y="30765750"/>
+          <a:ext cx="2643505" cy="1999615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2415,7 +2415,9 @@
       <c r="F22" s="22">
         <v>40</v>
       </c>
-      <c r="G22" s="21"/>
+      <c r="G22" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="H22" s="23"/>
     </row>
     <row r="23" ht="165" customHeight="1" spans="2:8">
@@ -2432,7 +2434,9 @@
       <c r="F23" s="9">
         <v>40</v>
       </c>
-      <c r="G23" s="20"/>
+      <c r="G23" s="20" t="s">
+        <v>13</v>
+      </c>
       <c r="H23" s="8"/>
     </row>
     <row r="24" ht="165" customHeight="1"/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -1666,19 +1666,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2869565</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>2089785</xdr:rowOff>
+      <xdr:colOff>2729230</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2056765</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPr id="8" name="图片 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1691,8 +1691,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2543175" y="28641675"/>
-          <a:ext cx="2726690" cy="2061210"/>
+          <a:off x="2486025" y="30765750"/>
+          <a:ext cx="2643505" cy="1999615"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1708,19 +1708,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2085340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2729230</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>2056765</xdr:rowOff>
+      <xdr:colOff>2743835</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2000250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1733,8 +1733,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2486025" y="30765750"/>
-          <a:ext cx="2643505" cy="1999615"/>
+          <a:off x="2466975" y="28602940"/>
+          <a:ext cx="2677160" cy="2010410"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/四足-姚旋-5套/四足-姚旋-5套.xlsx
+++ b/四足-姚旋-5套/四足-姚旋-5套.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HTDW_4438\四足-姚旋-5套\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>零件名称：</t>
   </si>
@@ -120,6 +125,9 @@
   </si>
   <si>
     <t>大腿限位块</t>
+  </si>
+  <si>
+    <t>钣金快拆垫块</t>
   </si>
 </sst>
 </file>
@@ -148,6 +156,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -157,13 +172,6 @@
       <b/>
       <sz val="48"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -874,16 +882,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -895,25 +906,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -922,14 +933,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1288,384 +1296,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2851150</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>2049145</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="图片 17"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2447925" y="9810750"/>
-          <a:ext cx="2803525" cy="1991995"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2912110</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>2063115</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="图片 20"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2457450" y="11906250"/>
-          <a:ext cx="2854960" cy="2005965"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2894965</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>2076450</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="图片 27"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2419350" y="16087725"/>
-          <a:ext cx="2875915" cy="2028825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2908300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>2060575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="图片 28"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2466975" y="18183225"/>
-          <a:ext cx="2841625" cy="2012950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2940050</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>2080260</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="图片 29"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2447925" y="20269200"/>
-          <a:ext cx="2892425" cy="2042160"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2912110</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2052320</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="图片 31"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2428875" y="24431625"/>
-          <a:ext cx="2883535" cy="2042795"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2870200</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>2071370</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="图片 32"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2400300" y="26565225"/>
-          <a:ext cx="2870200" cy="2023745"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2886710</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>2004695</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2667000" y="22355175"/>
-          <a:ext cx="2620010" cy="1976120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2794635</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>2049145</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2457450" y="13944600"/>
-          <a:ext cx="2737485" cy="2049145"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -1684,7 +1314,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
+        <a:blip r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1726,7 +1356,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
+        <a:blip r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1735,6 +1365,426 @@
         <a:xfrm>
           <a:off x="2466975" y="28602940"/>
           <a:ext cx="2677160" cy="2010410"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2886710</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2038985</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="图片 23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="20231100"/>
+          <a:ext cx="2886710" cy="2038985"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2919730</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2066925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="9772650"/>
+          <a:ext cx="2881630" cy="2047875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2851785</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>2019935</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="22326600"/>
+          <a:ext cx="2851785" cy="2019935"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2878455</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2070100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2447925" y="24488775"/>
+          <a:ext cx="2830830" cy="2003425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2870200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>2056765</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="图片 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2419350" y="16078200"/>
+          <a:ext cx="2851150" cy="2018665"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2906395</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>2048510</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="图片 20"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="11849100"/>
+          <a:ext cx="2906395" cy="2048510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2880995</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2040255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="图片 24"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="13944600"/>
+          <a:ext cx="2880995" cy="2040255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2964815</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="图片 18"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="32804100"/>
+          <a:ext cx="2964815" cy="2099310"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2929890</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2087880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="18135600"/>
+          <a:ext cx="2929890" cy="2087880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2837815</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2001520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2400300" y="26517600"/>
+          <a:ext cx="2837815" cy="2001520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2024,7 +2074,7 @@
     <col min="9" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:7">
+    <row r="1" ht="13.5" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2037,7 +2087,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="13.5" spans="1:8">
+    <row r="2" ht="13.5" spans="1:21">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -2047,7 +2097,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" ht="13.5" spans="1:8">
+    <row r="3" ht="13.5" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2061,13 +2111,13 @@
       <c r="G3" s="1"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" ht="13.5" spans="1:8">
+    <row r="4" ht="13.5" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2076,7 +2126,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" ht="13.5" spans="1:8">
+    <row r="5" ht="13.5" spans="1:21">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
@@ -2086,7 +2136,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" ht="13.5" spans="1:8">
+    <row r="6" ht="13.5" spans="1:21">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -2121,325 +2171,343 @@
       <c r="H7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
     </row>
-    <row r="8" ht="13.5" spans="1:8">
+    <row r="8" ht="13.5" spans="1:21">
       <c r="A8" s="1"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="6"/>
+      <c r="H8" s="7"/>
     </row>
-    <row r="9" ht="165" customHeight="1" spans="1:8">
+    <row r="9" ht="165" customHeight="1" spans="1:21">
       <c r="A9" s="1"/>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9">
+      <c r="C9" s="9"/>
+      <c r="D9" s="10">
         <v>2</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <v>5</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <v>10</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="12"/>
     </row>
-    <row r="10" ht="165" customHeight="1" spans="1:8">
+    <row r="10" ht="165" customHeight="1" spans="1:21">
       <c r="A10" s="1"/>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="9">
+      <c r="C10" s="13"/>
+      <c r="D10" s="10">
         <v>2</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <v>5</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="10">
         <v>10</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="11"/>
     </row>
-    <row r="11" ht="165" customHeight="1" spans="2:8">
-      <c r="B11" s="7" t="s">
+    <row r="11" ht="165" customHeight="1" spans="1:21">
+      <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="9">
+      <c r="C11" s="14"/>
+      <c r="D11" s="10">
         <v>2</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="10">
         <v>5</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="10">
         <v>10</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="10"/>
+      <c r="H11" s="11"/>
     </row>
-    <row r="12" ht="165" customHeight="1" spans="1:8">
+    <row r="12" ht="165" customHeight="1" spans="1:21">
       <c r="A12" s="1"/>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="9">
+      <c r="C12" s="13"/>
+      <c r="D12" s="10">
         <v>2</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <v>5</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="10">
         <v>10</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="10"/>
+      <c r="H12" s="11"/>
     </row>
-    <row r="13" ht="165" customHeight="1" spans="1:8">
+    <row r="13" ht="165" customHeight="1" spans="1:21">
       <c r="A13" s="1"/>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="9">
+      <c r="C13" s="13"/>
+      <c r="D13" s="10">
         <v>8</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <v>5</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="10">
         <v>40</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="13"/>
+      <c r="H13" s="14"/>
     </row>
-    <row r="14" ht="165" customHeight="1" spans="1:8">
+    <row r="14" ht="165" customHeight="1" spans="1:21">
       <c r="A14" s="1"/>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="9">
+      <c r="C14" s="13"/>
+      <c r="D14" s="10">
         <v>2</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <v>5</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="10">
         <v>10</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="13"/>
+      <c r="H14" s="14"/>
     </row>
-    <row r="15" ht="165" customHeight="1" spans="1:11">
+    <row r="15" ht="165" customHeight="1" spans="1:21">
       <c r="A15" s="1"/>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="9">
+      <c r="C15" s="13"/>
+      <c r="D15" s="10">
         <v>4</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <v>5</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="10">
         <v>20</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="13"/>
+      <c r="H15" s="14"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" ht="165" customHeight="1" spans="1:11">
+    <row r="16" ht="165" customHeight="1" spans="1:21">
       <c r="A16" s="1"/>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="9">
+      <c r="C16" s="13"/>
+      <c r="D16" s="10">
         <v>4</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <v>5</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="10">
         <v>20</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="13"/>
+      <c r="H16" s="14"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" ht="165" customHeight="1" spans="1:11">
       <c r="A17" s="1"/>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="9">
+      <c r="C17" s="13"/>
+      <c r="D17" s="10">
         <v>2</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>5</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="10">
         <v>10</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="13"/>
+      <c r="H17" s="14"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" ht="165" customHeight="1" spans="2:8">
-      <c r="B18" s="7" t="s">
+    <row r="18" ht="165" customHeight="1" spans="1:11">
+      <c r="B18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="9">
+      <c r="C18" s="13"/>
+      <c r="D18" s="10">
         <v>4</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <v>5</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="10">
         <v>20</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="13"/>
+      <c r="H18" s="14"/>
     </row>
-    <row r="19" ht="165" customHeight="1" spans="2:8">
-      <c r="B19" s="7" t="s">
+    <row r="19" ht="165" customHeight="1" spans="1:11">
+      <c r="B19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="9">
+      <c r="C19" s="13"/>
+      <c r="D19" s="10">
         <v>8</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <v>5</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="10">
         <v>40</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="13"/>
+      <c r="H19" s="14"/>
     </row>
-    <row r="20" ht="165" customHeight="1" spans="2:8">
-      <c r="B20" s="15" t="s">
+    <row r="20" ht="165" customHeight="1" spans="1:11">
+      <c r="B20" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17">
+      <c r="C20" s="17"/>
+      <c r="D20" s="18">
         <v>4</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <v>5</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="18">
         <v>20</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="19"/>
+      <c r="H20" s="20"/>
     </row>
-    <row r="21" ht="165" customHeight="1" spans="2:8">
-      <c r="B21" s="20" t="s">
+    <row r="21" ht="165" customHeight="1" spans="1:11">
+      <c r="B21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9">
+      <c r="C21" s="9"/>
+      <c r="D21" s="10">
         <v>2</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <v>5</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="10">
         <v>10</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="8"/>
+      <c r="H21" s="9"/>
     </row>
-    <row r="22" ht="165" customHeight="1" spans="2:8">
-      <c r="B22" s="21" t="s">
+    <row r="22" ht="165" customHeight="1" spans="1:11">
+      <c r="B22" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="22">
+      <c r="C22" s="22"/>
+      <c r="D22" s="23">
         <v>8</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <v>5</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="23">
         <v>40</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="23"/>
+      <c r="H22" s="24"/>
     </row>
-    <row r="23" ht="165" customHeight="1" spans="2:8">
-      <c r="B23" s="20" t="s">
+    <row r="23" ht="165" customHeight="1" spans="1:11">
+      <c r="B23" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="9">
+      <c r="C23" s="21"/>
+      <c r="D23" s="10">
         <v>8</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>5</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>40</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="9"/>
     </row>
-    <row r="24" ht="165" customHeight="1"/>
+    <row r="24" ht="165" customHeight="1" spans="1:11">
+      <c r="B24" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="10">
+        <v>4</v>
+      </c>
+      <c r="E24" s="10">
+        <v>5</v>
+      </c>
+      <c r="F24" s="10">
+        <v>20</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="9"/>
+    </row>
     <row r="25" ht="165" customHeight="1"/>
     <row r="26" ht="165" customHeight="1"/>
     <row r="27" ht="165" customHeight="1"/>
